--- a/Preformato_Importar_Maestra.xlsx
+++ b/Preformato_Importar_Maestra.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MAESTRA" sheetId="1" r:id="Rff21ebaea60d4374"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BD-MAESTRA" sheetId="1" r:id="R4a8f9df851854459"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -13,9 +13,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="2">
+  <x:numFmts count="1">
     <x:numFmt numFmtId="200" formatCode="@"/>
-    <x:numFmt numFmtId="201" formatCode="0"/>
   </x:numFmts>
   <x:fonts count="2">
     <x:font>
@@ -38,7 +37,7 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="0F172A"/>
+        <x:fgColor rgb="1F4E78"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -49,7 +48,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="13">
+  <x:cellXfs count="17">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -68,35 +67,32 @@
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
     <x:xf numFmtId="200" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="200" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="201" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
 </x:styleSheet>
-</file>
-
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaMaestraImportar" displayName="TablaMaestraImportar" ref="A1:G4" headerRowCount="1">
-  <x:tableColumns count="7">
-    <x:tableColumn id="1" name="CODIGO"/>
-    <x:tableColumn id="2" name="DESCRIPCION"/>
-    <x:tableColumn id="3" name="CANTIDAD"/>
-    <x:tableColumn id="4" name="CATEGORIA"/>
-    <x:tableColumn id="5" name="UNIDAD"/>
-    <x:tableColumn id="6" name="STATUS"/>
-    <x:tableColumn id="7" name="UBICACION"/>
-  </x:tableColumns>
-  <x:tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
-</x:table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -248,114 +244,508 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="34" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="6.590000152587891" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18.299999237060547" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="8.609999656677246" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="9.289999961853027" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="6.730000019073486" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="5.920000076293945" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="9.289999961853027" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1">
-      <x:c r="A1" s="10" t="str">
+    <x:row r="1" ht="24" customHeight="1">
+      <x:c r="A1" s="14" t="str">
         <x:v>CODIGO</x:v>
       </x:c>
-      <x:c r="B1" s="5" t="str">
+      <x:c r="B1" s="10" t="str">
         <x:v>DESCRIPCION</x:v>
       </x:c>
-      <x:c r="C1" s="12" t="str">
+      <x:c r="C1" s="10" t="str">
         <x:v>CANTIDAD</x:v>
       </x:c>
-      <x:c r="D1" s="5" t="str">
+      <x:c r="D1" s="10" t="str">
         <x:v>CATEGORIA</x:v>
       </x:c>
-      <x:c r="E1" s="5" t="str">
+      <x:c r="E1" s="10" t="str">
         <x:v>UNIDAD</x:v>
       </x:c>
-      <x:c r="F1" s="5" t="str">
+      <x:c r="F1" s="10" t="str">
         <x:v>STATUS</x:v>
       </x:c>
-      <x:c r="G1" s="5" t="str">
+      <x:c r="G1" s="10" t="str">
         <x:v>UBICACION</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" t="str">
+      <x:c r="A2" s="16" t="str">
         <x:v>000123</x:v>
       </x:c>
-      <x:c r="B2" t="str">
-        <x:v>PRODUCTO EJEMPLO 1</x:v>
-      </x:c>
-      <x:c r="C2" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D2" t="str">
+      <x:c r="B2" s="11" t="str">
+        <x:v>PRODUCTO EJEMPLO</x:v>
+      </x:c>
+      <x:c r="C2" s="11" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="D2" s="11" t="str">
         <x:v>GENERAL</x:v>
       </x:c>
-      <x:c r="E2" t="str">
+      <x:c r="E2" s="11" t="str">
         <x:v>UN</x:v>
       </x:c>
-      <x:c r="F2" t="str">
+      <x:c r="F2" s="11" t="str">
         <x:v>ACTIVO</x:v>
       </x:c>
-      <x:c r="G2" t="str">
-        <x:v>A-01-01</x:v>
+      <x:c r="G2" s="11" t="str">
+        <x:v>A-01</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" t="str">
+      <x:c r="A3" s="16" t="str">
         <x:v>000124</x:v>
       </x:c>
-      <x:c r="B3" t="str">
+      <x:c r="B3" s="11" t="str">
         <x:v>PRODUCTO EJEMPLO 2</x:v>
       </x:c>
-      <x:c r="C3" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D3" t="str">
+      <x:c r="C3" s="11" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D3" s="11" t="str">
         <x:v>GENERAL</x:v>
       </x:c>
-      <x:c r="E3" t="str">
-        <x:v>CJ</x:v>
-      </x:c>
-      <x:c r="F3" t="str">
+      <x:c r="E3" s="11" t="str">
+        <x:v>UN</x:v>
+      </x:c>
+      <x:c r="F3" s="11" t="str">
         <x:v>ACTIVO</x:v>
       </x:c>
-      <x:c r="G3" t="str">
-        <x:v>B-02-03</x:v>
+      <x:c r="G3" s="11" t="str">
+        <x:v>A-02</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" t="str">
-        <x:v>000125</x:v>
-      </x:c>
-      <x:c r="B4" t="str">
-        <x:v>PRODUCTO EJEMPLO 3</x:v>
-      </x:c>
-      <x:c r="C4" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D4" t="str">
-        <x:v>REPUESTOS</x:v>
-      </x:c>
-      <x:c r="E4" t="str">
-        <x:v>UN</x:v>
-      </x:c>
-      <x:c r="F4" t="str">
-        <x:v>INACTIVO</x:v>
-      </x:c>
-      <x:c r="G4" t="str"/>
+      <x:c r="A4" s="16"/>
+      <x:c r="B4" s="11"/>
+      <x:c r="C4" s="11"/>
+      <x:c r="D4" s="11"/>
+      <x:c r="E4" s="11"/>
+      <x:c r="F4" s="11"/>
+      <x:c r="G4" s="11"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="16"/>
+      <x:c r="B5" s="11"/>
+      <x:c r="C5" s="11"/>
+      <x:c r="D5" s="11"/>
+      <x:c r="E5" s="11"/>
+      <x:c r="F5" s="11"/>
+      <x:c r="G5" s="11"/>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="16"/>
+      <x:c r="B6" s="11"/>
+      <x:c r="C6" s="11"/>
+      <x:c r="D6" s="11"/>
+      <x:c r="E6" s="11"/>
+      <x:c r="F6" s="11"/>
+      <x:c r="G6" s="11"/>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="16"/>
+      <x:c r="B7" s="11"/>
+      <x:c r="C7" s="11"/>
+      <x:c r="D7" s="11"/>
+      <x:c r="E7" s="11"/>
+      <x:c r="F7" s="11"/>
+      <x:c r="G7" s="11"/>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="16"/>
+      <x:c r="B8" s="11"/>
+      <x:c r="C8" s="11"/>
+      <x:c r="D8" s="11"/>
+      <x:c r="E8" s="11"/>
+      <x:c r="F8" s="11"/>
+      <x:c r="G8" s="11"/>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="16"/>
+      <x:c r="B9" s="11"/>
+      <x:c r="C9" s="11"/>
+      <x:c r="D9" s="11"/>
+      <x:c r="E9" s="11"/>
+      <x:c r="F9" s="11"/>
+      <x:c r="G9" s="11"/>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="16"/>
+      <x:c r="B10" s="11"/>
+      <x:c r="C10" s="11"/>
+      <x:c r="D10" s="11"/>
+      <x:c r="E10" s="11"/>
+      <x:c r="F10" s="11"/>
+      <x:c r="G10" s="11"/>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="16"/>
+      <x:c r="B11" s="11"/>
+      <x:c r="C11" s="11"/>
+      <x:c r="D11" s="11"/>
+      <x:c r="E11" s="11"/>
+      <x:c r="F11" s="11"/>
+      <x:c r="G11" s="11"/>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="16"/>
+      <x:c r="B12" s="11"/>
+      <x:c r="C12" s="11"/>
+      <x:c r="D12" s="11"/>
+      <x:c r="E12" s="11"/>
+      <x:c r="F12" s="11"/>
+      <x:c r="G12" s="11"/>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="16"/>
+      <x:c r="B13" s="11"/>
+      <x:c r="C13" s="11"/>
+      <x:c r="D13" s="11"/>
+      <x:c r="E13" s="11"/>
+      <x:c r="F13" s="11"/>
+      <x:c r="G13" s="11"/>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="16"/>
+      <x:c r="B14" s="11"/>
+      <x:c r="C14" s="11"/>
+      <x:c r="D14" s="11"/>
+      <x:c r="E14" s="11"/>
+      <x:c r="F14" s="11"/>
+      <x:c r="G14" s="11"/>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="16"/>
+      <x:c r="B15" s="11"/>
+      <x:c r="C15" s="11"/>
+      <x:c r="D15" s="11"/>
+      <x:c r="E15" s="11"/>
+      <x:c r="F15" s="11"/>
+      <x:c r="G15" s="11"/>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="16"/>
+      <x:c r="B16" s="11"/>
+      <x:c r="C16" s="11"/>
+      <x:c r="D16" s="11"/>
+      <x:c r="E16" s="11"/>
+      <x:c r="F16" s="11"/>
+      <x:c r="G16" s="11"/>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="16"/>
+      <x:c r="B17" s="11"/>
+      <x:c r="C17" s="11"/>
+      <x:c r="D17" s="11"/>
+      <x:c r="E17" s="11"/>
+      <x:c r="F17" s="11"/>
+      <x:c r="G17" s="11"/>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="16"/>
+      <x:c r="B18" s="11"/>
+      <x:c r="C18" s="11"/>
+      <x:c r="D18" s="11"/>
+      <x:c r="E18" s="11"/>
+      <x:c r="F18" s="11"/>
+      <x:c r="G18" s="11"/>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="16"/>
+      <x:c r="B19" s="11"/>
+      <x:c r="C19" s="11"/>
+      <x:c r="D19" s="11"/>
+      <x:c r="E19" s="11"/>
+      <x:c r="F19" s="11"/>
+      <x:c r="G19" s="11"/>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="16"/>
+      <x:c r="B20" s="11"/>
+      <x:c r="C20" s="11"/>
+      <x:c r="D20" s="11"/>
+      <x:c r="E20" s="11"/>
+      <x:c r="F20" s="11"/>
+      <x:c r="G20" s="11"/>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="16"/>
+      <x:c r="B21" s="11"/>
+      <x:c r="C21" s="11"/>
+      <x:c r="D21" s="11"/>
+      <x:c r="E21" s="11"/>
+      <x:c r="F21" s="11"/>
+      <x:c r="G21" s="11"/>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="16"/>
+      <x:c r="B22" s="11"/>
+      <x:c r="C22" s="11"/>
+      <x:c r="D22" s="11"/>
+      <x:c r="E22" s="11"/>
+      <x:c r="F22" s="11"/>
+      <x:c r="G22" s="11"/>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="16"/>
+      <x:c r="B23" s="11"/>
+      <x:c r="C23" s="11"/>
+      <x:c r="D23" s="11"/>
+      <x:c r="E23" s="11"/>
+      <x:c r="F23" s="11"/>
+      <x:c r="G23" s="11"/>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="16"/>
+      <x:c r="B24" s="11"/>
+      <x:c r="C24" s="11"/>
+      <x:c r="D24" s="11"/>
+      <x:c r="E24" s="11"/>
+      <x:c r="F24" s="11"/>
+      <x:c r="G24" s="11"/>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="16"/>
+      <x:c r="B25" s="11"/>
+      <x:c r="C25" s="11"/>
+      <x:c r="D25" s="11"/>
+      <x:c r="E25" s="11"/>
+      <x:c r="F25" s="11"/>
+      <x:c r="G25" s="11"/>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="16"/>
+      <x:c r="B26" s="11"/>
+      <x:c r="C26" s="11"/>
+      <x:c r="D26" s="11"/>
+      <x:c r="E26" s="11"/>
+      <x:c r="F26" s="11"/>
+      <x:c r="G26" s="11"/>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="16"/>
+      <x:c r="B27" s="11"/>
+      <x:c r="C27" s="11"/>
+      <x:c r="D27" s="11"/>
+      <x:c r="E27" s="11"/>
+      <x:c r="F27" s="11"/>
+      <x:c r="G27" s="11"/>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="16"/>
+      <x:c r="B28" s="11"/>
+      <x:c r="C28" s="11"/>
+      <x:c r="D28" s="11"/>
+      <x:c r="E28" s="11"/>
+      <x:c r="F28" s="11"/>
+      <x:c r="G28" s="11"/>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="16"/>
+      <x:c r="B29" s="11"/>
+      <x:c r="C29" s="11"/>
+      <x:c r="D29" s="11"/>
+      <x:c r="E29" s="11"/>
+      <x:c r="F29" s="11"/>
+      <x:c r="G29" s="11"/>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="16"/>
+      <x:c r="B30" s="11"/>
+      <x:c r="C30" s="11"/>
+      <x:c r="D30" s="11"/>
+      <x:c r="E30" s="11"/>
+      <x:c r="F30" s="11"/>
+      <x:c r="G30" s="11"/>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="16"/>
+      <x:c r="B31" s="11"/>
+      <x:c r="C31" s="11"/>
+      <x:c r="D31" s="11"/>
+      <x:c r="E31" s="11"/>
+      <x:c r="F31" s="11"/>
+      <x:c r="G31" s="11"/>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="16"/>
+      <x:c r="B32" s="11"/>
+      <x:c r="C32" s="11"/>
+      <x:c r="D32" s="11"/>
+      <x:c r="E32" s="11"/>
+      <x:c r="F32" s="11"/>
+      <x:c r="G32" s="11"/>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="16"/>
+      <x:c r="B33" s="11"/>
+      <x:c r="C33" s="11"/>
+      <x:c r="D33" s="11"/>
+      <x:c r="E33" s="11"/>
+      <x:c r="F33" s="11"/>
+      <x:c r="G33" s="11"/>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="16"/>
+      <x:c r="B34" s="11"/>
+      <x:c r="C34" s="11"/>
+      <x:c r="D34" s="11"/>
+      <x:c r="E34" s="11"/>
+      <x:c r="F34" s="11"/>
+      <x:c r="G34" s="11"/>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" s="16"/>
+      <x:c r="B35" s="11"/>
+      <x:c r="C35" s="11"/>
+      <x:c r="D35" s="11"/>
+      <x:c r="E35" s="11"/>
+      <x:c r="F35" s="11"/>
+      <x:c r="G35" s="11"/>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" s="16"/>
+      <x:c r="B36" s="11"/>
+      <x:c r="C36" s="11"/>
+      <x:c r="D36" s="11"/>
+      <x:c r="E36" s="11"/>
+      <x:c r="F36" s="11"/>
+      <x:c r="G36" s="11"/>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" s="16"/>
+      <x:c r="B37" s="11"/>
+      <x:c r="C37" s="11"/>
+      <x:c r="D37" s="11"/>
+      <x:c r="E37" s="11"/>
+      <x:c r="F37" s="11"/>
+      <x:c r="G37" s="11"/>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" s="16"/>
+      <x:c r="B38" s="11"/>
+      <x:c r="C38" s="11"/>
+      <x:c r="D38" s="11"/>
+      <x:c r="E38" s="11"/>
+      <x:c r="F38" s="11"/>
+      <x:c r="G38" s="11"/>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" s="16"/>
+      <x:c r="B39" s="11"/>
+      <x:c r="C39" s="11"/>
+      <x:c r="D39" s="11"/>
+      <x:c r="E39" s="11"/>
+      <x:c r="F39" s="11"/>
+      <x:c r="G39" s="11"/>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" s="16"/>
+      <x:c r="B40" s="11"/>
+      <x:c r="C40" s="11"/>
+      <x:c r="D40" s="11"/>
+      <x:c r="E40" s="11"/>
+      <x:c r="F40" s="11"/>
+      <x:c r="G40" s="11"/>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" s="16"/>
+      <x:c r="B41" s="11"/>
+      <x:c r="C41" s="11"/>
+      <x:c r="D41" s="11"/>
+      <x:c r="E41" s="11"/>
+      <x:c r="F41" s="11"/>
+      <x:c r="G41" s="11"/>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" s="16"/>
+      <x:c r="B42" s="11"/>
+      <x:c r="C42" s="11"/>
+      <x:c r="D42" s="11"/>
+      <x:c r="E42" s="11"/>
+      <x:c r="F42" s="11"/>
+      <x:c r="G42" s="11"/>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" s="16"/>
+      <x:c r="B43" s="11"/>
+      <x:c r="C43" s="11"/>
+      <x:c r="D43" s="11"/>
+      <x:c r="E43" s="11"/>
+      <x:c r="F43" s="11"/>
+      <x:c r="G43" s="11"/>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" s="16"/>
+      <x:c r="B44" s="11"/>
+      <x:c r="C44" s="11"/>
+      <x:c r="D44" s="11"/>
+      <x:c r="E44" s="11"/>
+      <x:c r="F44" s="11"/>
+      <x:c r="G44" s="11"/>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" s="16"/>
+      <x:c r="B45" s="11"/>
+      <x:c r="C45" s="11"/>
+      <x:c r="D45" s="11"/>
+      <x:c r="E45" s="11"/>
+      <x:c r="F45" s="11"/>
+      <x:c r="G45" s="11"/>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" s="16"/>
+      <x:c r="B46" s="11"/>
+      <x:c r="C46" s="11"/>
+      <x:c r="D46" s="11"/>
+      <x:c r="E46" s="11"/>
+      <x:c r="F46" s="11"/>
+      <x:c r="G46" s="11"/>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" s="16"/>
+      <x:c r="B47" s="11"/>
+      <x:c r="C47" s="11"/>
+      <x:c r="D47" s="11"/>
+      <x:c r="E47" s="11"/>
+      <x:c r="F47" s="11"/>
+      <x:c r="G47" s="11"/>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48" s="16"/>
+      <x:c r="B48" s="11"/>
+      <x:c r="C48" s="11"/>
+      <x:c r="D48" s="11"/>
+      <x:c r="E48" s="11"/>
+      <x:c r="F48" s="11"/>
+      <x:c r="G48" s="11"/>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49" s="16"/>
+      <x:c r="B49" s="11"/>
+      <x:c r="C49" s="11"/>
+      <x:c r="D49" s="11"/>
+      <x:c r="E49" s="11"/>
+      <x:c r="F49" s="11"/>
+      <x:c r="G49" s="11"/>
+    </x:row>
+    <x:row r="50">
+      <x:c r="A50" s="16"/>
+      <x:c r="B50" s="11"/>
+      <x:c r="C50" s="11"/>
+      <x:c r="D50" s="11"/>
+      <x:c r="E50" s="11"/>
+      <x:c r="F50" s="11"/>
+      <x:c r="G50" s="11"/>
     </x:row>
   </x:sheetData>
-  <x:dataValidations count="1">
-    <x:dataValidation type="list" sqref="F2:F500">
-      <x:formula1>"ACTIVO,INACTIVO,DESCONTINUADO"</x:formula1>
-    </x:dataValidation>
-  </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R482ae8ba2dc24320"/>
-  </x:tableParts>
 </x:worksheet>
 </file>